--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0002T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0002T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.60997339818628</v>
+        <v>2.04912067720527</v>
       </c>
       <c r="D2" t="n">
-        <v>6.223681816498316</v>
+        <v>1.011348295180976</v>
       </c>
       <c r="E2" t="n">
-        <v>9.125972934384619</v>
+        <v>1.482970601837501</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7792328237935213</v>
+        <v>0.1266253338664471</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.86191926695552</v>
+        <v>5.015061880880272</v>
       </c>
       <c r="D3" t="n">
-        <v>7.782147464085359</v>
+        <v>1.264598962913871</v>
       </c>
       <c r="E3" t="n">
-        <v>9.125972934384619</v>
+        <v>1.482970601837501</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7792328237935213</v>
+        <v>0.1266253338664471</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
